--- a/02_Data_Analysis/data/top_disagreements_feature_attribution.xlsx
+++ b/02_Data_Analysis/data/top_disagreements_feature_attribution.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">presentation_score</t>
   </si>
   <si>
-    <t xml:space="preserve">Rank</t>
+    <t xml:space="preserve">Bi_feature_rank</t>
   </si>
   <si>
     <t xml:space="preserve">known_peptide</t>
